--- a/data/final/series/comexstat_soja_exceto_semeadura_imp_kg.xlsx
+++ b/data/final/series/comexstat_soja_exceto_semeadura_imp_kg.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B77"/>
+  <dimension ref="A1:B78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1029,7 +1029,7 @@
         <v>46234</v>
       </c>
       <c r="B76" t="n">
-        <v>62866000</v>
+        <v>61696410</v>
       </c>
     </row>
     <row r="77">
@@ -1038,6 +1038,14 @@
       </c>
       <c r="B77" t="n">
         <v>109088024</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B78" t="n">
+        <v>117130000</v>
       </c>
     </row>
   </sheetData>
